--- a/Config/BindingConfig.xlsx
+++ b/Config/BindingConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25080" windowHeight="10920"/>
+    <workbookView windowWidth="22140" windowHeight="9630"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -82,16 +82,112 @@
     <t>描述</t>
   </si>
   <si>
-    <t>雷霆嘎巴</t>
+    <t>潜质力量</t>
+  </si>
+  <si>
+    <t>BronzeBook</t>
+  </si>
+  <si>
+    <t>每回合开始,英雄攻击力会永久+1,可一直叠加</t>
+  </si>
+  <si>
+    <t>命运</t>
+  </si>
+  <si>
+    <t>SilverBook</t>
+  </si>
+  <si>
+    <t>每次攻击时,提供的倍率永久+0.5,可一直叠加</t>
+  </si>
+  <si>
+    <t>雷霆斩击</t>
   </si>
   <si>
     <t>Leiting</t>
   </si>
   <si>
-    <t>1|0.4</t>
-  </si>
-  <si>
-    <t>每次伤害附加1次40%的雷霆伤害</t>
+    <t>1|5</t>
+  </si>
+  <si>
+    <t>触发暴击时,会对目标造成1次英雄当前攻击力500%的雷霆斩击</t>
+  </si>
+  <si>
+    <t>幸运点数</t>
+  </si>
+  <si>
+    <t>LuckyNumber</t>
+  </si>
+  <si>
+    <t>攻击时,会随机将本次亮出数字牌的其中1张在后续永久获得强化,在后续亮出的牌中每包含1张强化过的数字牌,就有10%的概率使自身无视比牌规则直接获胜</t>
+  </si>
+  <si>
+    <t>权力</t>
+  </si>
+  <si>
+    <t>NobilityPower</t>
+  </si>
+  <si>
+    <t>每亮出1次人头牌,就会叠加1层[权力],达到15层后敌人亮牌将有50%概率不会攻击自己,而是攻击其他敌人</t>
+  </si>
+  <si>
+    <t>注魔硬币</t>
+  </si>
+  <si>
+    <t>MagicCoin</t>
+  </si>
+  <si>
+    <t>进行的每次消费行为都会使你后续造成的伤害永久提高2.5%</t>
+  </si>
+  <si>
+    <t>鲜血仪式</t>
+  </si>
+  <si>
+    <t>BloodCeremony</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>每次回复生命时,如果场上有敌人,则会对所有敌人造成1次当前恢复生命值的伤害</t>
+  </si>
+  <si>
+    <t>沉默诅咒</t>
+  </si>
+  <si>
+    <t>CurseSilence</t>
+  </si>
+  <si>
+    <t>1|1</t>
+  </si>
+  <si>
+    <t>拥有1次复活机会,且每次受到伤害后都会使对方在下回合受到[沉默](无法比牌,直接判负)</t>
+  </si>
+  <si>
+    <t>夺命追击</t>
+  </si>
+  <si>
+    <t>DoubleAttack</t>
+  </si>
+  <si>
+    <t>攻击时会额外追加1次,且追加的攻击也会触发其他效果(比如暴击),但伤害效益降低至60%</t>
+  </si>
+  <si>
+    <t>属性强化</t>
+  </si>
+  <si>
+    <t>RandomAttribute</t>
+  </si>
+  <si>
+    <t>每次使用技能都会随机获得以下属性之一:攻击力永久+3,生命+10,暴击率永久+1%</t>
+  </si>
+  <si>
+    <t>技能回响</t>
+  </si>
+  <si>
+    <t>DisableSkill</t>
+  </si>
+  <si>
+    <t>你的技能会被禁用,但不影响技能次数带来的各种收益,且你的牌型无论输赢,总是会对对方造成技能总次数x攻击力的伤害</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1161,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="5.54166666666667" style="1" customWidth="1"/>
@@ -1145,22 +1241,172 @@
       <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="6" customFormat="1" spans="1:6">
+      <c r="B6" s="2">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
       </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="6" customFormat="1"/>
-    <row r="7" customFormat="1"/>
-    <row r="8" customFormat="1"/>
-    <row r="9" customFormat="1"/>
-    <row r="10" customFormat="1"/>
-    <row r="11" customFormat="1"/>
+    <row r="7" customFormat="1" spans="1:6">
+      <c r="B7" s="2">
+        <v>103</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:6">
+      <c r="B8" s="2">
+        <v>104</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:6">
+      <c r="B9" s="2">
+        <v>105</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="2">
+        <v>106</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="2">
+        <v>107</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="2">
+        <v>108</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="2">
+        <v>109</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="2">
+        <v>110</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="2">
+        <v>111</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/BindingConfig.xlsx
+++ b/Config/BindingConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -118,6 +118,9 @@
     <t>LuckyNumber</t>
   </si>
   <si>
+    <t>1|0.1</t>
+  </si>
+  <si>
     <t>攻击时,会随机将本次亮出数字牌的其中1张在后续永久获得强化,在后续亮出的牌中每包含1张强化过的数字牌,就有10%的概率使自身无视比牌规则直接获胜</t>
   </si>
   <si>
@@ -127,6 +130,9 @@
     <t>NobilityPower</t>
   </si>
   <si>
+    <t>1|15|0.5</t>
+  </si>
+  <si>
     <t>每亮出1次人头牌,就会叠加1层[权力],达到15层后敌人亮牌将有50%概率不会攻击自己,而是攻击其他敌人</t>
   </si>
   <si>
@@ -136,6 +142,9 @@
     <t>MagicCoin</t>
   </si>
   <si>
+    <t>0.025</t>
+  </si>
+  <si>
     <t>进行的每次消费行为都会使你后续造成的伤害永久提高2.5%</t>
   </si>
   <si>
@@ -160,7 +169,7 @@
     <t>1|1</t>
   </si>
   <si>
-    <t>拥有1次复活机会,且每次受到伤害后都会使对方在下回合受到[沉默](无法比牌,直接判负)</t>
+    <t>拥有1次复活机会,且复活后</t>
   </si>
   <si>
     <t>夺命追击</t>
@@ -169,13 +178,19 @@
     <t>DoubleAttack</t>
   </si>
   <si>
-    <t>攻击时会额外追加1次,且追加的攻击也会触发其他效果(比如暴击),但伤害效益降低至60%</t>
+    <t>1|-0.4</t>
+  </si>
+  <si>
+    <t>攻击时会额外追加1次,且追加的攻击也会触发其他效果(比如暴击),但伤害降低40%</t>
   </si>
   <si>
     <t>属性强化</t>
   </si>
   <si>
     <t>RandomAttribute</t>
+  </si>
+  <si>
+    <t>3|10|0.01</t>
   </si>
   <si>
     <t>每次使用技能都会随机获得以下属性之一:攻击力永久+3,生命+10,暴击率永久+1%</t>
@@ -1295,9 +1310,11 @@
       <c r="D8" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:6">
@@ -1305,16 +1322,16 @@
         <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1322,13 +1339,16 @@
         <v>106</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1336,16 +1356,16 @@
         <v>107</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1353,16 +1373,16 @@
         <v>108</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1370,13 +1390,16 @@
         <v>109</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1384,13 +1407,16 @@
         <v>110</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1398,13 +1424,16 @@
         <v>111</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Config/BindingConfig.xlsx
+++ b/Config/BindingConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22140" windowHeight="9630"/>
+    <workbookView windowWidth="12510" windowHeight="11235"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -203,6 +203,65 @@
   </si>
   <si>
     <t>你的技能会被禁用,但不影响技能次数带来的各种收益,且你的牌型无论输赢,总是会对对方造成技能总次数x攻击力的伤害</t>
+  </si>
+  <si>
+    <t>资本注入</t>
+  </si>
+  <si>
+    <t>Capital</t>
+  </si>
+  <si>
+    <t>5|-0.2</t>
+  </si>
+  <si>
+    <r>
+      <t>每回合开始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>金币</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>且商店中圣物与槽位购买价格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-20%</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -215,13 +274,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -366,6 +431,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -688,137 +759,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -827,6 +898,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1176,7 +1250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="5.54166666666667" style="1" customWidth="1"/>
@@ -1436,6 +1510,23 @@
         <v>56</v>
       </c>
     </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="2">
+        <v>112</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/BindingConfig.xlsx
+++ b/Config/BindingConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12510" windowHeight="11235"/>
+    <workbookView windowWidth="13710" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -202,7 +202,7 @@
     <t>DisableSkill</t>
   </si>
   <si>
-    <t>你的技能会被禁用,但不影响技能次数带来的各种收益,且你的牌型无论输赢,总是会对对方造成技能总次数x攻击力的伤害</t>
+    <t>你的技能会被禁用,但不影响技能次数带来的各种收益,每次比牌后对方会受到(技能次数与当前攻击力相乘)伤害</t>
   </si>
   <si>
     <t>资本注入</t>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>每回合开始</t>
     </r>
     <r>
